--- a/data/trans_dic/IP1005-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen anomalía congénita</t>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,88</t>
+          <t>0,57; 5,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,54</t>
+          <t>0,29; 2,67</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,48</t>
+          <t>0,27; 2,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,74</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,8</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,97</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,5</t>
+          <t>0,22; 1,42</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
     </row>
@@ -1337,22 +1338,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,81</t>
+          <t>0,07; 0,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,89</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1362,22 +1363,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,16</t>
+          <t>0,2; 1,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,45</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,5</t>
+          <t>0,1; 0,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,81</t>
+          <t>0,22; 0,81</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3280</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3843</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2539</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3707</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>640; 5854</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3923</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>642; 5833</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3662</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3423</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3827</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3383</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3009</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>606; 5950</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3001</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2998</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3466</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>950; 6169</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2929</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4534</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3420</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3124</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3339</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4684</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>443; 5240</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>605; 5714</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4375</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4748</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1390; 8333</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>641; 6269</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1326; 7341</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3042; 11182</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1005-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Clase-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,19</t>
+          <t>0,56; 4,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,67</t>
+          <t>0,29; 2,52</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,66</t>
+          <t>0,27; 2,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,42</t>
+          <t>0,22; 1,58</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1338,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,78</t>
+          <t>0,07; 0,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,09; 0,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,17</t>
+          <t>0,19; 1,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,53</t>
+          <t>0,08; 0,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,81</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3280</t>
+          <t>0; 3302</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3843</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2539</t>
+          <t>0; 2506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3707</t>
+          <t>0; 2729</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>640; 5854</t>
+          <t>630; 5561</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 3754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>642; 5833</t>
+          <t>640; 5516</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3662</t>
+          <t>0; 2774</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3539</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3827</t>
+          <t>0; 3404</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3383</t>
+          <t>0; 3798</t>
         </is>
       </c>
     </row>
@@ -2128,17 +2128,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3235</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3009</t>
+          <t>0; 3492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>606; 5950</t>
+          <t>605; 5552</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2153,22 +2153,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3001</t>
+          <t>0; 2603</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2998</t>
+          <t>0; 3037</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3466</t>
+          <t>0; 3482</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>950; 6169</t>
+          <t>961; 6856</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2929</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4534</t>
+          <t>0; 4642</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3420</t>
+          <t>0; 3005</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3110</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3339</t>
+          <t>0; 3085</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4684</t>
+          <t>0; 4477</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>443; 5240</t>
+          <t>442; 4786</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>605; 5714</t>
+          <t>605; 5744</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4548</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4748</t>
+          <t>0; 4738</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1390; 8333</t>
+          <t>1359; 7670</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>641; 6269</t>
+          <t>641; 6202</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1326; 7341</t>
+          <t>1122; 7381</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3042; 11182</t>
+          <t>3074; 10984</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1005-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -740,27 +740,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,57; 4,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,52</t>
+          <t>0,29; 2,54</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,48</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,34; 2,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,58</t>
+          <t>0,24; 1,5</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,67</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0,19; 1,16</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,71</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,86</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,66</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,07; 0,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,08</t>
+          <t>0,09; 0,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,53</t>
+          <t>0,06; 0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,24; 0,81</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1538,22 +1538,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1591,22 +1591,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>661</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3302</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3972</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 3329</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2506</t>
+          <t>0; 3373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>637; 5499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2729</t>
+          <t>0; 2699</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>630; 5561</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3754</t>
+          <t>0; 4370</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>640; 5516</t>
+          <t>638; 5544</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1985,12 +1985,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2774</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3539</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3404</t>
+          <t>0; 3396</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3798</t>
+          <t>0; 4291</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2319</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3492</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>605; 5552</t>
+          <t>0; 3154</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3228</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2603</t>
+          <t>755; 5537</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3037</t>
+          <t>0; 3230</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3482</t>
+          <t>0; 4188</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>961; 6856</t>
+          <t>1041; 6534</t>
         </is>
       </c>
     </row>
@@ -2238,22 +2238,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>632</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>0; 3142</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 3176</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4642</t>
+          <t>0; 4575</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>602</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3216</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2979</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2855</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3441</t>
+          <t>0; 3292</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3085</t>
+          <t>0; 2779</t>
         </is>
       </c>
     </row>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2319</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4477</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>442; 4786</t>
+          <t>0; 4758</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>605; 5744</t>
+          <t>1342; 8256</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4548</t>
+          <t>0; 4493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4738</t>
+          <t>443; 5476</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1359; 7670</t>
+          <t>602; 5985</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>641; 6202</t>
+          <t>640; 5911</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1122; 7381</t>
+          <t>886; 6919</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3074; 10984</t>
+          <t>3288; 11137</t>
         </is>
       </c>
     </row>
